--- a/WROS_Canonical_Backlog_S001-401.xlsx
+++ b/WROS_Canonical_Backlog_S001-401.xlsx
@@ -25504,7 +25504,7 @@
       </c>
       <c r="O312" s="8" t="inlineStr">
         <is>
-          <t>RETIRED — merged into S-309</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P312" s="8" t="inlineStr">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="O313" s="8" t="inlineStr">
         <is>
-          <t>RETIRED — folded into AI Activity Feed / Recruiter Copilot (S-061)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P313" s="8" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="O314" s="8" t="inlineStr">
         <is>
-          <t>RETIRED — folded into Auto Create Job from Demand (S-289)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P314" s="8" t="inlineStr">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="O315" s="8" t="inlineStr">
         <is>
-          <t>RETIRED — merged into S-306</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P315" s="8" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="O316" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P316" s="2" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="O317" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P317" s="2" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="O318" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P318" s="2" t="inlineStr">
@@ -26064,7 +26064,7 @@
       </c>
       <c r="O319" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P319" s="2" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="O320" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P320" s="2" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="O325" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P325" s="2" t="inlineStr">
@@ -26624,7 +26624,7 @@
       </c>
       <c r="O326" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P326" s="2" t="inlineStr">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="O388" s="14" t="inlineStr">
         <is>
-          <t>Ready for Build</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P388" s="14" t="inlineStr">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="O389" s="14" t="inlineStr">
         <is>
-          <t>Ready for Build</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P389" s="14" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="O390" s="14" t="inlineStr">
         <is>
-          <t>Ready for Build</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P390" s="14" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="O402" s="14" t="inlineStr">
         <is>
-          <t>BLOCKED — Awaiting Finance/CA Requirements Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P402" s="14" t="inlineStr">
@@ -32659,7 +32659,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P403" t="inlineStr">
@@ -32724,7 +32724,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P404" t="inlineStr">
